--- a/release/notes/plateau-studio/plateau-web/release-notes/v3.0.29/xlsxToJson_Sample_ExcelFile.xlsx
+++ b/release/notes/plateau-studio/plateau-web/release-notes/v3.0.29/xlsxToJson_Sample_ExcelFile.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Temp\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\STechQ\cdn\release\notes\plateau-studio\plateau-web\release-notes\v3.0.29\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04B2082A-A72F-450C-A58D-390761354BBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5867DE6C-74F2-4130-915F-1BAFD6340DE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="hus1" sheetId="1" r:id="rId1"/>
-    <sheet name="hus2" sheetId="2" r:id="rId2"/>
+    <sheet name="page1" sheetId="1" r:id="rId1"/>
+    <sheet name="page2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>A</t>
   </si>
@@ -37,10 +37,25 @@
     <t>C</t>
   </si>
   <si>
-    <t>sdsa</t>
-  </si>
-  <si>
-    <t>dsads</t>
+    <t>yıldız 1</t>
+  </si>
+  <si>
+    <t>yıldız 2</t>
+  </si>
+  <si>
+    <t>ay 1</t>
+  </si>
+  <si>
+    <t>ay 2</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>F</t>
   </si>
 </sst>
 </file>
@@ -386,10 +401,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="1">
-        <v>12356.36</v>
+        <v>19876.36</v>
       </c>
       <c r="C2" s="2">
-        <v>45765</v>
+        <v>45301</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -397,10 +412,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="1">
-        <v>87512637.560000002</v>
+        <v>47812637.560000002</v>
       </c>
       <c r="C3" s="2">
-        <v>45797</v>
+        <v>45646</v>
       </c>
     </row>
   </sheetData>
@@ -420,18 +435,18 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B2" s="1">
         <v>12356.36</v>
@@ -442,7 +457,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B3" s="1">
         <v>87512637.560000002</v>
